--- a/data/final_rapport_data.xlsx
+++ b/data/final_rapport_data.xlsx
@@ -981,7 +981,16 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="25" t="n"/>
+      <c r="A3" s="25" t="inlineStr">
+        <is>
+          <t>NOVOCIB Rapport d'essai 260621-2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>260621-2</t>
+        </is>
+      </c>
       <c r="C3" s="25" t="n">
         <v>46194</v>
       </c>

--- a/data/final_rapport_data.xlsx
+++ b/data/final_rapport_data.xlsx
@@ -1261,7 +1261,16 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="25" t="n"/>
+      <c r="A5" s="25" t="inlineStr">
+        <is>
+          <t>NOVOCIB Rapport d'essai 260621-4</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>260621-4</t>
+        </is>
+      </c>
       <c r="C5" s="25" t="n">
         <v>46194</v>
       </c>

--- a/data/final_rapport_data.xlsx
+++ b/data/final_rapport_data.xlsx
@@ -1683,7 +1683,16 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="25" t="n"/>
+      <c r="A8" s="25" t="inlineStr">
+        <is>
+          <t>NOVOCIB Rapport d'essai 260621-7</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>260621-7</t>
+        </is>
+      </c>
       <c r="C8" s="25" t="n">
         <v>46194</v>
       </c>
